--- a/docs/02_基本設計/01_機能・画面一覧/KF-BD-002_画面一覧・画面遷移.xlsx
+++ b/docs/02_基本設計/01_機能・画面一覧/KF-BD-002_画面一覧・画面遷移.xlsx
@@ -70,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -92,11 +92,44 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,6 +149,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -493,6 +527,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -501,6 +538,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -512,7 +551,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -525,7 +564,7 @@
           <t>KF-BD-002</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -535,10 +574,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -551,7 +590,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -564,8 +603,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -612,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -671,6 +712,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007 パスワード変更を追加。SCR-001 の概要と遷移（初期パスワード時の SCR-007 誘導、401 での自動復帰）を更新</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -684,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -739,7 +803,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワードで認証</t>
+          <t>メールアドレスとパスワードで認証。失敗時のエラー表示、ロック中（E-017）の表示。初期パスワードの利用者は認証後 SCR-007 へ</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -1177,6 +1241,33 @@
       <c r="E18" s="8" t="inlineStr">
         <is>
           <t>F-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>現在のパスワードと新しいパスワード（確認入力あり）を入力して変更。初期パスワードの利用者は変更が済むまで他画面へ進めない</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>F-12</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1241,7 +1332,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>認証成功時</t>
+          <t>認証成功時（初期パスワードのままの利用者は SCR-007 へ）</t>
         </is>
       </c>
     </row>
@@ -1562,6 +1653,94 @@
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>処理完了時、元の一覧へ戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>ログイン成功（mustChangePassword=true）</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワードのまま。変更が済むまで他画面へ遷移できない（画面側ガード）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>全画面（ヘッダー）</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>「パスワード変更」を選択</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>ログイン後の全ロール</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更に成功</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007（同一画面）</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>自動遷移しない。成功メッセージ I-008 を表示し、入力欄を空にする。ホームへはヘッダーの「ホーム」から移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>全画面</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>API が 401 を返す（トークン期限切れ・不正）</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>ログイン情報を破棄して自動的にログイン画面へ戻る</t>
         </is>
       </c>
     </row>

--- a/docs/02_基本設計/01_機能・画面一覧/KF-BD-002_画面一覧・画面遷移.xlsx
+++ b/docs/02_基本設計/01_機能・画面一覧/KF-BD-002_画面一覧・画面遷移.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +69,13 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -125,11 +130,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +161,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,7 +591,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -653,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -735,6 +752,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>実装（router/index.js・views・AppLayout）と照合。SCR-108 通知一覧を新設。SCR-101〜103（/home 1 画面）、SCR-104/105（/requests/new 共用）、SCR-106（/requests・/requests/:id）、SCR-202（申請詳細と共用）、SCR-301（SCR-201 と共用）の実装上の対応を記載。画面一覧に実装ルート・ビュー列を追加し、対象ロールを実装に合わせて修正。画面遷移を左メニュー・パスワード変更後の再ログイン等に合わせて全面更新</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>SCR-109 休憩・離席修正申請を追加（/requests/new を SCR-104・105・109 で共用）。SCR-102 の休憩・離席ボタン、SCR-103 の休憩・離席列、SCR-104 の対象日初期値・両方必須、SCR-106・202 の「処理なし」表示、SCR-201 の申請種別絞込、SCR-302・306 の部署一覧API取得を概要に反映。画面遷移に、休憩・離席ボタン、打刻修正リンク（未実装）、初期パスワード時のメニュー無効表示を追加</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -748,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -756,32 +819,44 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>画面ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>画面名</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>対象ロール</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>概要</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>関連機能ID</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>実装ルート</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>実装（ビュー）・備考</t>
         </is>
       </c>
     </row>
@@ -803,375 +878,515 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワードで認証。失敗時のエラー表示、ロック中（E-017）の表示。初期パスワードの利用者は認証後 SCR-007 へ</t>
+          <t>メールアドレスとパスワードで認証。失敗時のエラー表示、ロック中（E-017）の表示。初期パスワードの利用者は認証後 SCR-007 へ。パスワード変更後はメッセージ（I-008）を表示</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-01, F-13</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>LoginView</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>現在のパスワードと新しいパスワード（確認入力あり）を入力して変更。初期パスワードの利用者は変更が済むまで他画面へ進めない（左メニューは無効表示で案内文を出す。サーバー側も E-019 で拒否）。成功後はログイン画面へ戻る</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>/password</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>ChangePasswordView。ヘッダーの「パスワード変更」からも開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
           <t>SCR-101</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>ホーム</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>今日の打刻状況、申請状況、休暇残日数、通知の要約</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>F-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>SCR-102</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>打刻</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>従業員</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>出勤・退勤ボタン。本日の打刻時刻を表示</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>ログイン後の最初の画面。実装は打刻（SCR-102）・月次勤怠（SCR-103）と同一画面。申請状況・休暇残日数・通知の要約を並べる独立のホームは未実装</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>F-02</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>HomeView（SCR-101〜103 を 1 画面に集約）。休暇残日数は SCR-107、通知は SCR-108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>SCR-103</t>
+          <t>SCR-102</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>月次勤怠一覧</t>
+          <t>打刻</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>月ごとの打刻履歴、勤務時間、残業時間</t>
+          <t>出勤・退勤ボタン、休憩・離席ボタン（開始／終了を兼用）。本日の打刻時刻、休憩中・離席中の案内、本日の休憩・離席の区間を表示</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>F-02</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>HomeView（上段の打刻カード）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>SCR-104</t>
+          <t>SCR-103</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>打刻修正申請</t>
+          <t>月次勤怠一覧</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>打刻漏れ・誤りの修正を理由付きで申請</t>
+          <t>月ごとの打刻履歴（出勤・退勤・休憩・離席の区間）、勤務時間、残業時間（前月・翌月へ切替。未来月は不可）</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>HomeView（下段の月次一覧）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>SCR-105</t>
+          <t>SCR-104</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>休暇申請</t>
+          <t>打刻修正申請</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>休暇種別・期間・理由を入力して申請。残日数を表示</t>
+          <t>打刻漏れ・誤りの修正を理由付きで申請（対象日（初期値は当日）・修正後の出勤／退勤（両方必須）・理由）。申請する／下書き保存</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>F-04</t>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>/requests/new</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>RequestFormView（申請種別「打刻修正申請」。SCR-105・SCR-109 と同一画面）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>SCR-106</t>
+          <t>SCR-105</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>申請一覧・詳細</t>
+          <t>休暇申請</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>自分の申請状況と承認履歴。取下げ・再提出</t>
+          <t>休暇種別・取得単位・期間・理由を入力して申請。選択した種別の残日数を表示。申請する／下書き保存</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>F-05</t>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>/requests/new</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>RequestFormView（申請種別「休暇申請」。SCR-104・SCR-109 と同一画面）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>SCR-107</t>
+          <t>SCR-106</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>休暇残日数</t>
+          <t>申請一覧・詳細</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>年次有給休暇の付与・消化・残日数、年5日取得義務の進捗</t>
+          <t>自分の申請一覧（状態で絞込）と詳細・承認履歴（取下げ・差戻し・却下で打ち切られた未処理の段は「処理なし」）。提出（下書き・差戻し）・取下げ</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>/requests（一覧）、/requests/:id（詳細）</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>RequestListView / RequestDetailView。差戻しの内容修正画面は無い</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>SCR-201</t>
+          <t>SCR-107</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>承認待ち一覧</t>
+          <t>休暇残日数</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>上長・管理者</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>自分が承認すべき申請の一覧</t>
+          <t>休暇種別ごとの付与・使用・残日数と付与行の内訳、年5日取得義務の進捗、次回付与予定日</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>/leave</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>LeaveBalanceView</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-108</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>承認詳細</t>
+          <t>通知一覧</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>上長・管理者</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>申請内容を確認し、承認・差戻し・却下（コメント必須）</t>
+          <t>自分の通知（最新 50 件）を新しい順に表示。クリックで既読化し、申請に紐づく通知は申請詳細へ遷移。ヘッダーのベルに未読件数を表示（60 秒ごとに更新）</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-11</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>NotificationListView（2026/10/05 追加。API-019）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>SCR-203</t>
+          <t>SCR-109</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>部下の勤怠・休暇一覧</t>
+          <t>休憩・離席修正申請</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>上長</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>部下の勤怠状況と休暇取得状況の閲覧</t>
+          <t>休憩・離席の打刻漏れ・終了の押し忘れを理由付きで申請（対象日（初期値は当日）・種別（休憩／離席）・開始・終了・理由）。申請する／下書き保存。承認（上長 → 管理者）されると打刻へ反映し、勤務時間を再計算</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>/requests/new</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>RequestFormView（申請種別「休憩・離席修正申請」。SCR-104・SCR-105 と同一画面。2026/10/05 追加）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>SCR-301</t>
+          <t>SCR-201</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>最終承認一覧</t>
+          <t>承認待ち一覧</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>上長・管理者</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>上長承認済みの申請を最終承認（SCR-202を共用）</t>
+          <t>自分が処理できる承認ステップの一覧（申請種別（休暇・打刻修正・休憩離席修正）・承認段階で絞込）。一覧上で承認・差戻し・却下（コメント入力ダイアログ）が可能</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>F-06</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>/approvals</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>ApprovalListView（SCR-301 と共用）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>SCR-302</t>
+          <t>SCR-202</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>ユーザー管理</t>
+          <t>承認詳細</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>上長・管理者</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>ユーザー・ロール・所属・承認ルートの登録・変更</t>
+          <t>申請内容（休暇・打刻修正・休憩離席修正）・承認履歴（「処理なし」を含む）を確認し、承認・差戻し・却下（コメント必須は差戻し・却下）</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>F-08</t>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>/requests/:id</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>RequestDetailView（申請者の SCR-106 詳細と共用。処理可能な承認者にだけ操作ボタンを表示）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>SCR-303</t>
+          <t>SCR-203</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>休暇種別マスタ</t>
+          <t>部下の勤怠・休暇一覧</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>上長</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>休暇種別と日数ルールの設定</t>
+          <t>直属の部下の月次集計（出勤日数・勤務時間・残業時間・休暇日数）。残業 45 時間超は赤字表示。管理者は利用不可</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>F-09</t>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>/manager/summary</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>ManagerSummaryView（メニュー名「部下の勤怠集計」）。個別の勤怠一覧は無い</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>SCR-304</t>
+          <t>SCR-301</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>祝日カレンダー</t>
+          <t>最終承認一覧</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1181,24 +1396,34 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>祝日・会社休日の登録</t>
+          <t>上長承認済みの申請の最終承認。専用画面は無く、SCR-201 の承認段階「2段目」の絞込で代用（SCR-202 を共用）</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>F-09</t>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>/approvals</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>ApprovalListView（SCR-201 と同一。専用ルート・専用メニューなし）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>SCR-305</t>
+          <t>SCR-302</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>休暇付与管理</t>
+          <t>ユーザー管理</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1208,24 +1433,34 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>年次有給休暇の付与・調整</t>
+          <t>ユーザー・ロール・所属・上長の登録・変更・無効化、パスワード再設定。部署の選択肢は GET /api/departments から取得。初期・再設定パスワードは12〜72文字・英字と数字を含む</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-08</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>/admin/users</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>AdminUserView</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>SCR-306</t>
+          <t>SCR-303</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>月次集計</t>
+          <t>休暇種別マスタ</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1235,39 +1470,133 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>全社の勤怠・休暇集計とCSV出力</t>
+          <t>休暇種別と日数ルールの設定</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>F-09</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>/admin/leave-types</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>AdminLeaveTypeView</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-304</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>パスワード変更</t>
+          <t>祝日カレンダー</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>現在のパスワードと新しいパスワード（確認入力あり）を入力して変更。初期パスワードの利用者は変更が済むまで他画面へ進めない</t>
+          <t>祝日・会社休日の登録・削除（年単位）</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>F-12</t>
+          <t>F-09</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>/admin/holidays</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>AdminHolidayView（メニュー名「祝日・会社休日」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>SCR-305</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>休暇付与管理</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>従業員ごとの付与履歴の参照、年次有給休暇などの付与・日数調整</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>/admin/leave-grants</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>AdminLeaveGrantView</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>SCR-306</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>月次集計</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>全社・部署別の勤怠・休暇集計の表示とCSV出力。部署の選択肢は GET /api/departments から取得</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>F-10</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>/admin/reports</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>AdminReportView</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1339,408 +1668,578 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>SCR-001</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>「打刻」を選択</t>
+          <t>ログイン成功（mustChangePassword=true）</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>SCR-102</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr"/>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワード・管理者再設定直後。変更が済むまで他画面へ遷移できない（画面のルーターガード＋サーバー側 E-019）。移動後は左メニューが無効表示になり、案内文「パスワードを変更するとメニューが使えるようになります。」を表示する</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>全画面（左メニュー）</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>「月次勤怠」を選択</t>
+          <t>「打刻・勤怠」を選択</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>SCR-103</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr"/>
+          <t>SCR-101（打刻 SCR-102・月次勤怠 SCR-103 を含む）</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>SCR-102（打刻）</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>「休暇申請」を選択</t>
+          <t>「休憩開始／終了」「離席開始／終了」ボタンを押す</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>SCR-105</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
+          <t>SCR-102（同一画面）</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>/home。同一画面で当月の勤怠を再取得し、完了メッセージ・休憩中／離席中の案内・本日の区間・SCR-103 の「休憩・離席」列を更新する。開始中は退勤できない（E-022）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>SCR-101</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>「申請一覧」を選択</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>SCR-106</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SCR-102（打刻）</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>「打刻の修正はこちら」リンクを選択</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>SCR-104 / SCR-109</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>【未実装（今後対応）】現行はリンクが無い（案内文のみ）。「申請」メニュー → 新規申請 → 申請種別を選んで開く</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>全画面（左メニュー）</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>「休暇残日数」を選択</t>
+          <t>「申請」を選択</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>SCR-107</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
+          <t>SCR-106（一覧）</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>SCR-106（一覧）</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>「承認待ち」を選択</t>
+          <t>「新規申請」を選択</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>SCR-201</t>
+          <t>SCR-104 / SCR-105 / SCR-109</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>上長・管理者のみ</t>
+          <t>/requests/new。申請種別（休暇申請／打刻修正申請／休憩・離席修正申請）で切替</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>全画面（左メニュー）</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>「部下の勤怠」を選択</t>
+          <t>「休暇残日数」を選択</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>SCR-203</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>上長のみ</t>
-        </is>
-      </c>
+          <t>SCR-107</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>SCR-107</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>「最終承認」を選択</t>
+          <t>「休暇を申請する」を選択</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>SCR-301</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>管理者のみ</t>
-        </is>
-      </c>
+          <t>SCR-105</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>全画面（左メニュー／ヘッダーのベル）</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>管理メニューを選択</t>
+          <t>「通知」を選択</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>SCR-302〜306</t>
+          <t>SCR-108</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>管理者のみ</t>
+          <t>未読件数をバッジ表示</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>SCR-102</t>
+          <t>SCR-108</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>「打刻修正」を選択</t>
+          <t>申請に紐づく通知を選択</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>SCR-104</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr"/>
+          <t>SCR-106（詳細）</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>選択時に既読化。申請に紐づかない通知（休暇付与など）は遷移しない</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>SCR-104</t>
+          <t>全画面（左メニュー）</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>申請を提出</t>
+          <t>「承認待ち」を選択</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>SCR-106</t>
+          <t>SCR-201</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>提出成功時</t>
+          <t>上長・管理者のみ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>SCR-105</t>
+          <t>全画面（左メニュー）</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>申請を提出</t>
+          <t>「部下の勤怠集計」を選択</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>SCR-106</t>
+          <t>SCR-203</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>提出成功時</t>
+          <t>上長のみ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>SCR-106</t>
+          <t>全画面（左メニュー）</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>差戻し申請を修正して再提出</t>
+          <t>管理メニュー（月次集計・ユーザー管理・休暇付与・休暇種別・祝日・会社休日）を選択</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>SCR-105 / SCR-104</t>
+          <t>SCR-306 / SCR-302 / SCR-305 / SCR-303 / SCR-304</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>ステータスが差戻しの場合</t>
+          <t>管理者のみ。「最終承認」メニューは無い（SCR-301 は SCR-201 の 2 段目絞込）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>SCR-201</t>
+          <t>SCR-104 / SCR-105 / SCR-109</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>申請を選択</t>
+          <t>「申請する」「下書き保存」</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr"/>
+          <t>SCR-106（詳細）</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>成功時、作成した申請の詳細へ遷移</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>SCR-301</t>
+          <t>SCR-106（一覧）</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>申請を選択</t>
+          <t>行を選択</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr"/>
+          <t>SCR-106（詳細）</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>SCR-202</t>
+          <t>SCR-106（詳細）</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下を実行</t>
+          <t>「提出する」（下書き・差戻し）／「取下げ」</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>SCR-201 / SCR-301</t>
+          <t>SCR-106（詳細）</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>処理完了時、元の一覧へ戻る</t>
+          <t>同一画面で再読込し、完了メッセージを表示。差戻し内容の修正画面は無い</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>SCR-001</t>
+          <t>SCR-201</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ログイン成功（mustChangePassword=true）</t>
+          <t>「詳細」を選択</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-202</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>初期パスワードのまま。変更が済むまで他画面へ遷移できない（画面側ガード）</t>
+          <t>申請詳細（/requests/:id）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>全画面（ヘッダー）</t>
+          <t>SCR-201</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>「パスワード変更」を選択</t>
+          <t>承認・差戻し・却下を実行</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-201</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>ログイン後の全ロール</t>
+          <t>処理完了後、一覧を再読込（元の一覧に留まる）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-202</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>パスワード変更に成功</t>
+          <t>承認・差戻し・却下を実行</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>SCR-007（同一画面）</t>
+          <t>SCR-202</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>自動遷移しない。成功メッセージ I-008 を表示し、入力欄を空にする。ホームへはヘッダーの「ホーム」から移動</t>
+          <t>同一画面で再読込。「一覧へ戻る」で SCR-201（承認者）／SCR-106（申請者）へ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>SCR-301</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>申請を選択</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>SCR-202</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>SCR-201 と同一画面（承認段階の絞込のみ異なる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>全画面（左メニュー）</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワードの利用者が左メニューを押す</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>（遷移しない）</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>メニューは無効表示で押せない。URL を直接開いても /password（SCR-007）へ戻される</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>全画面（ヘッダー）</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>「パスワード変更」を選択</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>ログイン後の全ロール</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更に成功</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>トークンを破棄して /login?changed=1 へ遷移。ログイン画面に I-008 を表示。再ログインが必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>全画面（ヘッダー）</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>「ログアウト」を選択</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>トークン・利用者情報を破棄（サーバー側の失効はしない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>全画面</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>API が 401 を返す（トークン期限切れ・不正）</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>API が 401 を返す（トークン期限切れ・不正・ユーザー無効化）</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>SCR-001</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>ログイン情報を破棄して自動的にログイン画面へ戻る</t>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>ログイン情報を破棄して自動的にログイン画面へ戻る（メッセージ表示なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>未ログイン</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>認証が必要な画面の URL を開く</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>ルーターガード</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>全画面</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>権限のない画面・存在しない URL を開く</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>SCR-101</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>ルーターガードで /home へリダイレクト（権限エラー専用画面は無い）</t>
         </is>
       </c>
     </row>
